--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_h_3.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_h_3.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.01487275922747523</v>
+        <v>0.008339309008925929</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008425238155320435</v>
+        <v>0.008417747105701008</v>
       </c>
       <c r="C2" t="n">
-        <v>18888831</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>18888831</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>13861820</v>
+        <v>4624709</v>
       </c>
       <c r="L2" t="n">
-        <v>8179772</v>
+        <v>2697549</v>
       </c>
       <c r="M2" t="n">
-        <v>2110139</v>
+        <v>692891</v>
       </c>
       <c r="N2" t="n">
-        <v>112586</v>
+        <v>33806</v>
       </c>
       <c r="O2" t="n">
-        <v>1263554</v>
+        <v>419672</v>
       </c>
       <c r="P2" t="n">
-        <v>498960</v>
+        <v>162300</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999781847000122</v>
+        <v>0.9999383687973022</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9184644818305969</v>
+        <v>0.9112957119941711</v>
       </c>
       <c r="S2" t="n">
-        <v>0.830768883228302</v>
+        <v>0.8239706754684448</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7732647657394409</v>
+        <v>0.7699995040893555</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5749081969261169</v>
+        <v>0.5165953636169434</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8209037780761719</v>
+        <v>0.8106439709663391</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8790388107299805</v>
+        <v>0.8795841932296753</v>
       </c>
       <c r="X2" t="n">
-        <v>18888831</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,314 +742,314 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>18888831</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>14410974</v>
+        <v>4815402</v>
       </c>
       <c r="AG2" t="n">
-        <v>8878131</v>
+        <v>2970254</v>
       </c>
       <c r="AH2" t="n">
-        <v>2395233</v>
+        <v>799435</v>
       </c>
       <c r="AI2" t="n">
-        <v>176729</v>
+        <v>58995</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1376498</v>
+        <v>459097</v>
       </c>
       <c r="AK2" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566605687141418</v>
+        <v>0.9565494656562805</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112324118614197</v>
+        <v>0.9113017320632935</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581742644309998</v>
+        <v>0.8579359650611877</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6626757383346558</v>
+        <v>0.6623888611793518</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.902050256729126</v>
+        <v>0.9020065665245056</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314221143722534</v>
+        <v>0.9314266443252563</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.003536771952182805</v>
+        <v>0.001931859311724547</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002021116422987386</v>
+        <v>0.002018670822238358</v>
       </c>
       <c r="C3" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D3" t="n">
-        <v>13861820</v>
+        <v>4624709</v>
       </c>
       <c r="E3" t="n">
-        <v>1158154</v>
+        <v>398300</v>
       </c>
       <c r="F3" t="n">
-        <v>24381</v>
+        <v>4458</v>
       </c>
       <c r="G3" t="n">
-        <v>3403</v>
+        <v>660</v>
       </c>
       <c r="H3" t="n">
-        <v>776</v>
+        <v>205</v>
       </c>
       <c r="I3" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>29969957</v>
+        <v>10016233</v>
       </c>
       <c r="K3" t="n">
-        <v>32579691</v>
+        <v>10850735</v>
       </c>
       <c r="L3" t="n">
-        <v>37437287</v>
+        <v>12489116</v>
       </c>
       <c r="M3" t="n">
-        <v>45448076</v>
+        <v>15190512</v>
       </c>
       <c r="N3" t="n">
-        <v>48509043</v>
+        <v>16208837</v>
       </c>
       <c r="O3" t="n">
-        <v>47056914</v>
+        <v>15722392</v>
       </c>
       <c r="P3" t="n">
-        <v>48210694</v>
+        <v>16114080</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9211158156394958</v>
+        <v>0.9196625947952271</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8384643197059631</v>
+        <v>0.8264063596725464</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7556740641593933</v>
+        <v>0.743349552154541</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4218125939369202</v>
+        <v>0.3792929351329803</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8276823759078979</v>
+        <v>0.8242146968841553</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8605043292045593</v>
+        <v>0.8396231532096863</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>14410974</v>
+        <v>4815402</v>
       </c>
       <c r="Z3" t="n">
-        <v>591937</v>
+        <v>197896</v>
       </c>
       <c r="AA3" t="n">
-        <v>25520</v>
+        <v>8540</v>
       </c>
       <c r="AB3" t="n">
-        <v>20288</v>
+        <v>6789</v>
       </c>
       <c r="AC3" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>29970369</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>33157398</v>
+        <v>11082162</v>
       </c>
       <c r="AG3" t="n">
-        <v>38238679</v>
+        <v>12776309</v>
       </c>
       <c r="AH3" t="n">
-        <v>45670960</v>
+        <v>15265103</v>
       </c>
       <c r="AI3" t="n">
-        <v>48502329</v>
+        <v>16210402</v>
       </c>
       <c r="AJ3" t="n">
-        <v>47183115</v>
+        <v>15770546</v>
       </c>
       <c r="AK3" t="n">
-        <v>48239592</v>
+        <v>16123045</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576069712638855</v>
+        <v>0.957583487033844</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100493192672729</v>
+        <v>0.9099507331848145</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8577707409858704</v>
+        <v>0.8576524257659912</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6621295809745789</v>
+        <v>0.6619057655334473</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016655683517456</v>
+        <v>0.9016434550285339</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313610792160034</v>
+        <v>0.9313350915908813</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.04489973553449609</v>
+        <v>0.02908173215621476</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03188647610643539</v>
+        <v>0.03186393749853683</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1164810</v>
+        <v>425785</v>
       </c>
       <c r="E4" t="n">
-        <v>8179772</v>
+        <v>2697549</v>
       </c>
       <c r="F4" t="n">
-        <v>380187</v>
+        <v>131698</v>
       </c>
       <c r="G4" t="n">
-        <v>9427</v>
+        <v>2955</v>
       </c>
       <c r="H4" t="n">
-        <v>20151</v>
+        <v>5884</v>
       </c>
       <c r="I4" t="n">
-        <v>1312</v>
+        <v>321</v>
       </c>
       <c r="J4" t="n">
-        <v>412</v>
+        <v>389</v>
       </c>
       <c r="K4" t="n">
-        <v>1230565</v>
+        <v>450163</v>
       </c>
       <c r="L4" t="n">
-        <v>1666254</v>
+        <v>576292</v>
       </c>
       <c r="M4" t="n">
-        <v>618731</v>
+        <v>206968</v>
       </c>
       <c r="N4" t="n">
-        <v>83247</v>
+        <v>31634</v>
       </c>
       <c r="O4" t="n">
-        <v>275669</v>
+        <v>98030</v>
       </c>
       <c r="P4" t="n">
-        <v>68660</v>
+        <v>22219</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999890923500061</v>
+        <v>0.9999691843986511</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9197882413864136</v>
+        <v>0.9154599905014038</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8345988392829895</v>
+        <v>0.8251867294311523</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7643682360649109</v>
+        <v>0.7564399242401123</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4866027235984802</v>
+        <v>0.4374227523803711</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8242791295051575</v>
+        <v>0.8173730969429016</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8696727752685547</v>
+        <v>0.8591392636299133</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>609497</v>
+        <v>204218</v>
       </c>
       <c r="Z4" t="n">
-        <v>8878131</v>
+        <v>2970254</v>
       </c>
       <c r="AA4" t="n">
-        <v>247989</v>
+        <v>83015</v>
       </c>
       <c r="AB4" t="n">
-        <v>16406</v>
+        <v>5489</v>
       </c>
       <c r="AC4" t="n">
-        <v>3432</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>204</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>652858</v>
+        <v>218736</v>
       </c>
       <c r="AG4" t="n">
-        <v>864862</v>
+        <v>289099</v>
       </c>
       <c r="AH4" t="n">
-        <v>395847</v>
+        <v>132377</v>
       </c>
       <c r="AI4" t="n">
-        <v>89961</v>
+        <v>30069</v>
       </c>
       <c r="AJ4" t="n">
-        <v>149468</v>
+        <v>49876</v>
       </c>
       <c r="AK4" t="n">
-        <v>39762</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571335315704346</v>
+        <v>0.9570662379264832</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106404781341553</v>
+        <v>0.910625696182251</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579724431037903</v>
+        <v>0.8577942252159119</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6624025702476501</v>
+        <v>0.6621472835540771</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.901857852935791</v>
+        <v>0.9018250107765198</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313915967941284</v>
+        <v>0.9313808679580688</v>
       </c>
     </row>
     <row r="5">
@@ -1059,152 +1059,152 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>39009</v>
+        <v>14789</v>
       </c>
       <c r="E5" t="n">
-        <v>446672</v>
+        <v>155003</v>
       </c>
       <c r="F5" t="n">
-        <v>2110139</v>
+        <v>692891</v>
       </c>
       <c r="G5" t="n">
-        <v>38504</v>
+        <v>15700</v>
       </c>
       <c r="H5" t="n">
-        <v>150319</v>
+        <v>51558</v>
       </c>
       <c r="I5" t="n">
-        <v>7750</v>
+        <v>2179</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1187124</v>
+        <v>403993</v>
       </c>
       <c r="L5" t="n">
-        <v>1575887</v>
+        <v>566643</v>
       </c>
       <c r="M5" t="n">
-        <v>682254</v>
+        <v>239229</v>
       </c>
       <c r="N5" t="n">
-        <v>154324</v>
+        <v>55323</v>
       </c>
       <c r="O5" t="n">
-        <v>263063</v>
+        <v>89506</v>
       </c>
       <c r="P5" t="n">
-        <v>80886</v>
+        <v>31001</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999915957450867</v>
+        <v>0.9999761581420898</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9505172371864319</v>
+        <v>0.9476927518844604</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9336431622505188</v>
+        <v>0.9300084114074707</v>
       </c>
       <c r="T5" t="n">
-        <v>0.973372757434845</v>
+        <v>0.9726755619049072</v>
       </c>
       <c r="U5" t="n">
-        <v>0.995137631893158</v>
+        <v>0.9946748614311218</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9889737963676453</v>
+        <v>0.9885155558586121</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9969392418861389</v>
+        <v>0.9967408776283264</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>23924</v>
+        <v>8010</v>
       </c>
       <c r="Z5" t="n">
-        <v>254266</v>
+        <v>84966</v>
       </c>
       <c r="AA5" t="n">
-        <v>2395233</v>
+        <v>799435</v>
       </c>
       <c r="AB5" t="n">
-        <v>29769</v>
+        <v>9941</v>
       </c>
       <c r="AC5" t="n">
-        <v>87302</v>
+        <v>29135</v>
       </c>
       <c r="AD5" t="n">
-        <v>1899</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>637970</v>
+        <v>213300</v>
       </c>
       <c r="AG5" t="n">
-        <v>877528</v>
+        <v>293938</v>
       </c>
       <c r="AH5" t="n">
-        <v>397160</v>
+        <v>132685</v>
       </c>
       <c r="AI5" t="n">
-        <v>90181</v>
+        <v>30134</v>
       </c>
       <c r="AJ5" t="n">
-        <v>150119</v>
+        <v>50081</v>
       </c>
       <c r="AK5" t="n">
-        <v>39800</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735806584358215</v>
+        <v>0.9735427498817444</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643385410308838</v>
+        <v>0.9642956852912903</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837695360183716</v>
+        <v>0.9837679862976074</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963130354881287</v>
+        <v>0.9963132739067078</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.993868350982666</v>
+        <v>0.9938787817955017</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983716011047363</v>
+        <v>0.9983755350112915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>26621</v>
+        <v>9544</v>
       </c>
       <c r="E6" t="n">
-        <v>42251</v>
+        <v>17756</v>
       </c>
       <c r="F6" t="n">
-        <v>53240</v>
+        <v>16049</v>
       </c>
       <c r="G6" t="n">
-        <v>112586</v>
+        <v>33806</v>
       </c>
       <c r="H6" t="n">
-        <v>29944</v>
+        <v>11321</v>
       </c>
       <c r="I6" t="n">
-        <v>2242</v>
+        <v>633</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>19270</v>
+        <v>6452</v>
       </c>
       <c r="Z6" t="n">
-        <v>15989</v>
+        <v>5347</v>
       </c>
       <c r="AA6" t="n">
-        <v>32568</v>
+        <v>10875</v>
       </c>
       <c r="AB6" t="n">
-        <v>176729</v>
+        <v>58995</v>
       </c>
       <c r="AC6" t="n">
-        <v>20911</v>
+        <v>6979</v>
       </c>
       <c r="AD6" t="n">
-        <v>1443</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1263,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="E7" t="n">
-        <v>18260</v>
+        <v>4993</v>
       </c>
       <c r="F7" t="n">
-        <v>156929</v>
+        <v>53590</v>
       </c>
       <c r="G7" t="n">
-        <v>30495</v>
+        <v>11817</v>
       </c>
       <c r="H7" t="n">
-        <v>1263554</v>
+        <v>419672</v>
       </c>
       <c r="I7" t="n">
-        <v>57309</v>
+        <v>19078</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>2427</v>
+        <v>809</v>
       </c>
       <c r="AA7" t="n">
-        <v>88780</v>
+        <v>29617</v>
       </c>
       <c r="AB7" t="n">
-        <v>22703</v>
+        <v>7585</v>
       </c>
       <c r="AC7" t="n">
-        <v>1376498</v>
+        <v>459097</v>
       </c>
       <c r="AD7" t="n">
-        <v>36126</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>917</v>
+        <v>240</v>
       </c>
       <c r="F8" t="n">
-        <v>3994</v>
+        <v>1173</v>
       </c>
       <c r="G8" t="n">
-        <v>1418</v>
+        <v>502</v>
       </c>
       <c r="H8" t="n">
-        <v>74479</v>
+        <v>29062</v>
       </c>
       <c r="I8" t="n">
-        <v>498960</v>
+        <v>162300</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>990</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>795</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>37688</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
